--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2022_los_lagos_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2022_los_lagos_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 11:30</t>
+    <t xml:space="preserve">2026-09-09 19:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2022_los_lagos_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2022_los_lagos_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:06</t>
+    <t xml:space="preserve">2026-09-17 04:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2022_los_lagos_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2022_los_lagos_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 04:23</t>
+    <t xml:space="preserve">2026-09-25 11:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2022_los_lagos_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2022_los_lagos_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25 11:17</t>
+    <t xml:space="preserve">2026-09-26 23:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2022_los_lagos_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2022_los_lagos_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-26 23:50</t>
+    <t xml:space="preserve">2026-10-05 04:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
